--- a/data/trans_dic/P55$nadie-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P55$nadie-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 26,8</t>
+          <t>2,0; 22,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 17,07</t>
+          <t>2,09; 17,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,66</t>
+          <t>0,0; 20,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 15,73</t>
+          <t>2,49; 13,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 17,05</t>
+          <t>4,07; 18,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,55</t>
+          <t>1,34; 11,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 23,2</t>
+          <t>7,27; 22,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 10,5</t>
+          <t>2,36; 10,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 15,71</t>
+          <t>4,23; 15,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,61</t>
+          <t>2,48; 10,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 17,55</t>
+          <t>5,5; 17,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,67</t>
+          <t>3,23; 9,37</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,16</t>
+          <t>1,08; 9,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,0</t>
+          <t>0,0; 12,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,61</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,28</t>
+          <t>1,99; 8,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 10,36</t>
+          <t>2,57; 10,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,36</t>
+          <t>0,51; 4,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 10,24</t>
+          <t>2,72; 11,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,5</t>
+          <t>2,7; 6,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,1</t>
+          <t>2,63; 8,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,17</t>
+          <t>0,73; 5,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 8,24</t>
+          <t>2,04; 7,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,2</t>
+          <t>3,16; 6,24</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 10,58</t>
+          <t>2,12; 11,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 11,08</t>
+          <t>1,36; 10,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 8,92</t>
+          <t>3,06; 8,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,33</t>
+          <t>3,67; 10,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,78</t>
+          <t>0,82; 4,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 12,49</t>
+          <t>5,32; 12,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,09</t>
+          <t>3,04; 6,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,9</t>
+          <t>3,95; 9,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,38</t>
+          <t>1,52; 5,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 9,1</t>
+          <t>4,0; 9,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,26</t>
+          <t>3,61; 6,53</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7862</t>
         </is>
       </c>
     </row>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>880; 11199</t>
+          <t>837; 9318</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>902; 7761</t>
+          <t>951; 7866</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4908</t>
+          <t>0; 6297</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1532; 7930</t>
+          <t>1371; 7668</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2607; 11535</t>
+          <t>2753; 12395</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>945; 8056</t>
+          <t>934; 8328</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6219; 19058</t>
+          <t>5971; 18578</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1517; 7665</t>
+          <t>1901; 8333</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5138; 17189</t>
+          <t>4627; 16751</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2020; 12215</t>
+          <t>2853; 12663</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6421; 19920</t>
+          <t>6240; 20026</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4106; 11937</t>
+          <t>4385; 12698</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>17554</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>917; 7770</t>
+          <t>912; 7904</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 13088</t>
+          <t>0; 12214</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3249</t>
+          <t>0; 3955</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2122; 8833</t>
+          <t>2272; 10112</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4331; 16914</t>
+          <t>4196; 16468</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1078; 9146</t>
+          <t>1070; 10293</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4894; 18963</t>
+          <t>5038; 20549</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7175; 16580</t>
+          <t>7478; 18085</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5687; 20082</t>
+          <t>6521; 20773</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3196; 16054</t>
+          <t>2254; 16668</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5867; 22701</t>
+          <t>5623; 21342</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10892; 22437</t>
+          <t>12331; 24377</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23124</t>
+          <t>25416</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2724; 13387</t>
+          <t>2680; 14318</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2040; 16193</t>
+          <t>1985; 15764</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6573</t>
+          <t>0; 5968</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4722; 14007</t>
+          <t>5172; 14989</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8557; 23850</t>
+          <t>8471; 23526</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2238; 13353</t>
+          <t>2280; 13169</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14120; 33383</t>
+          <t>14223; 33820</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10249; 19982</t>
+          <t>10871; 23262</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13473; 31810</t>
+          <t>14130; 32718</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6426; 22914</t>
+          <t>6480; 23012</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14844; 35393</t>
+          <t>15546; 36057</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16054; 30365</t>
+          <t>19009; 34345</t>
         </is>
       </c>
     </row>
